--- a/ψ/lab/sample-docs/จำนวนวรรคใน พ.ร.บ. และระเบียบ.xlsx
+++ b/ψ/lab/sample-docs/จำนวนวรรคใน พ.ร.บ. และระเบียบ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mingsaksaengwilaipon/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mingsaksaengwilaipon/gnim-oracle/ψ/lab/sample-docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF528511-B107-8344-A7CD-EB1BAE0B22AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B5C6EC-9D1A-944D-AE4B-B2B67CDCD147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="620" windowWidth="25600" windowHeight="28180" activeTab="1" xr2:uid="{236B512D-08CD-F84F-850A-66C61E42A8FB}"/>
+    <workbookView xWindow="0" yWindow="940" windowWidth="20480" windowHeight="25700" xr2:uid="{236B512D-08CD-F84F-850A-66C61E42A8FB}"/>
   </bookViews>
   <sheets>
     <sheet name="พ.ร.บ." sheetId="1" r:id="rId1"/>
@@ -953,7 +953,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -969,7 +969,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -977,7 +977,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
